--- a/sale data 14 April.xlsx
+++ b/sale data 14 April.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/WORK/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E869CE0-9989-B249-A0BD-54A60FAAB842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C8F7F2-97E0-074C-955D-97DF75837F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="18840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="77">
   <si>
     <t>card_name</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>Commodity Picks</t>
+  </si>
+  <si>
+    <t>Lite Loyalty - 6399</t>
   </si>
 </sst>
 </file>
@@ -1055,16 +1058,30 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="A20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="3">
+        <v>60</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="G20" s="4">
+        <v>26999</v>
+      </c>
+      <c r="H20" s="4">
+        <v>6399</v>
+      </c>
       <c r="I20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1353,7 +1370,7 @@
         <v>89999</v>
       </c>
       <c r="H32" s="4">
-        <v>9999</v>
+        <v>8999</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>35</v>
@@ -1382,7 +1399,7 @@
         <v>89999</v>
       </c>
       <c r="H33" s="4">
-        <v>8999</v>
+        <v>9999</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>35</v>
